--- a/partial/sliding_window_results_window_3.xlsx
+++ b/partial/sliding_window_results_window_3.xlsx
@@ -463,13 +463,13 @@
         <v>29.35</v>
       </c>
       <c r="C2" t="n">
-        <v>28.88047081994445</v>
+        <v>30.08906540050407</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.4695291800555488</v>
+        <v>0.7390654005040673</v>
       </c>
       <c r="E2" t="n">
-        <v>0.220457650923636</v>
+        <v>0.5462176662222374</v>
       </c>
     </row>
     <row r="3">
@@ -480,13 +480,13 @@
         <v>29.37</v>
       </c>
       <c r="C3" t="n">
-        <v>28.79754100912948</v>
+        <v>29.78556385453234</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.5724589908705227</v>
+        <v>0.4155638545323406</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3277092962284971</v>
+        <v>0.1726933171937763</v>
       </c>
     </row>
     <row r="4">
@@ -497,13 +497,13 @@
         <v>29.54</v>
       </c>
       <c r="C4" t="n">
-        <v>28.72393905747945</v>
+        <v>29.2700097296191</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.8160609425205472</v>
+        <v>-0.2699902703808945</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6659554619075237</v>
+        <v>0.07289474610034853</v>
       </c>
     </row>
     <row r="5">
@@ -514,13 +514,13 @@
         <v>29.55</v>
       </c>
       <c r="C5" t="n">
-        <v>29.94445591304089</v>
+        <v>29.82163104762523</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3944559130408862</v>
+        <v>0.271631047625231</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1555954673329192</v>
+        <v>0.07378342603398054</v>
       </c>
     </row>
     <row r="6">
@@ -531,13 +531,13 @@
         <v>29.75</v>
       </c>
       <c r="C6" t="n">
-        <v>29.61782930945843</v>
+        <v>29.50887915476766</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1321706905415745</v>
+        <v>-0.2411208452323379</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01746909143823665</v>
+        <v>0.05813926200555704</v>
       </c>
     </row>
     <row r="7">
@@ -548,13 +548,13 @@
         <v>29.84</v>
       </c>
       <c r="C7" t="n">
-        <v>30.54245861807876</v>
+        <v>30.0574479233339</v>
       </c>
       <c r="D7" t="n">
-        <v>0.702458618078758</v>
+        <v>0.2174479233338964</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4934481101131183</v>
+        <v>0.04728359936222409</v>
       </c>
     </row>
     <row r="8">
@@ -565,13 +565,13 @@
         <v>29.81</v>
       </c>
       <c r="C8" t="n">
-        <v>30.40697447332623</v>
+        <v>29.93957089088588</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5969744733262274</v>
+        <v>0.1295708908858764</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3563785218031266</v>
+        <v>0.01678861576495968</v>
       </c>
     </row>
     <row r="9">
@@ -582,13 +582,13 @@
         <v>29.92</v>
       </c>
       <c r="C9" t="n">
-        <v>30.21982061576142</v>
+        <v>29.68718008544232</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2998206157614156</v>
+        <v>-0.2328199145576804</v>
       </c>
       <c r="E9" t="n">
-        <v>0.08989240163555441</v>
+        <v>0.05420511261464558</v>
       </c>
     </row>
     <row r="10">
@@ -599,13 +599,13 @@
         <v>29.98</v>
       </c>
       <c r="C10" t="n">
-        <v>29.49073496471589</v>
+        <v>29.61174624372592</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.489265035284113</v>
+        <v>-0.3682537562740791</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2393802747515644</v>
+        <v>0.1356108290099688</v>
       </c>
     </row>
     <row r="11">
@@ -616,13 +616,13 @@
         <v>30.04</v>
       </c>
       <c r="C11" t="n">
-        <v>29.76432767218155</v>
+        <v>29.61864572433147</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.2756723278184516</v>
+        <v>-0.4213542756685307</v>
       </c>
       <c r="E11" t="n">
-        <v>0.07599523232484386</v>
+        <v>0.1775394256241521</v>
       </c>
     </row>
     <row r="12">
@@ -633,13 +633,13 @@
         <v>30.21</v>
       </c>
       <c r="C12" t="n">
-        <v>29.2289763240952</v>
+        <v>29.69651013084202</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.981023675904801</v>
+        <v>-0.5134898691579828</v>
       </c>
       <c r="E12" t="n">
-        <v>0.962407452685768</v>
+        <v>0.2636718457278823</v>
       </c>
     </row>
     <row r="13">
@@ -650,13 +650,13 @@
         <v>30.22</v>
       </c>
       <c r="C13" t="n">
-        <v>29.64752027789943</v>
+        <v>29.9117261406573</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.5724797221005709</v>
+        <v>-0.3082738593426946</v>
       </c>
       <c r="E13" t="n">
-        <v>0.3277330322163468</v>
+        <v>0.09503277235403944</v>
       </c>
     </row>
     <row r="14">
@@ -667,13 +667,13 @@
         <v>30.38</v>
       </c>
       <c r="C14" t="n">
-        <v>29.41012243268786</v>
+        <v>30.20390420453156</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.9698775673121389</v>
+        <v>-0.1760957954684379</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9406624955753126</v>
+        <v>0.03100972918166191</v>
       </c>
     </row>
     <row r="15">
@@ -684,13 +684,13 @@
         <v>30.44</v>
       </c>
       <c r="C15" t="n">
-        <v>30.14218121153088</v>
+        <v>30.46567407497348</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.2978187884691224</v>
+        <v>0.02567407497347673</v>
       </c>
       <c r="E15" t="n">
-        <v>0.08869603076521584</v>
+        <v>0.0006591581257437044</v>
       </c>
     </row>
     <row r="16">
@@ -701,13 +701,13 @@
         <v>30.48</v>
       </c>
       <c r="C16" t="n">
-        <v>30.17853079185805</v>
+        <v>30.22834259137082</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.3014692081419525</v>
+        <v>-0.2516574086291818</v>
       </c>
       <c r="E16" t="n">
-        <v>0.09088368345773591</v>
+        <v>0.06333145131795501</v>
       </c>
     </row>
     <row r="17">
@@ -718,13 +718,13 @@
         <v>30.69</v>
       </c>
       <c r="C17" t="n">
-        <v>30.47421113686185</v>
+        <v>30.26397303977103</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.2157888631381546</v>
+        <v>-0.4260269602289668</v>
       </c>
       <c r="E17" t="n">
-        <v>0.04656483345445721</v>
+        <v>0.1814989708419337</v>
       </c>
     </row>
     <row r="18">
@@ -735,13 +735,13 @@
         <v>30.75</v>
       </c>
       <c r="C18" t="n">
-        <v>30.0327836856211</v>
+        <v>30.78538835040724</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.7172163143789021</v>
+        <v>0.03538835040723853</v>
       </c>
       <c r="E18" t="n">
-        <v>0.5143992416112562</v>
+        <v>0.0012523353445455</v>
       </c>
     </row>
     <row r="19">
@@ -752,13 +752,13 @@
         <v>30.94</v>
       </c>
       <c r="C19" t="n">
-        <v>30.48739069386338</v>
+        <v>30.67079586766802</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.4526093061366225</v>
+        <v>-0.2692041323319856</v>
       </c>
       <c r="E19" t="n">
-        <v>0.2048551840014749</v>
+        <v>0.07247086486461721</v>
       </c>
     </row>
     <row r="20">
@@ -769,13 +769,13 @@
         <v>30.95</v>
       </c>
       <c r="C20" t="n">
-        <v>30.80707348865126</v>
+        <v>30.81323862459335</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1429265113487403</v>
+        <v>-0.1367613754066461</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0204279876463216</v>
+        <v>0.01870367380311759</v>
       </c>
     </row>
     <row r="21">
@@ -786,13 +786,13 @@
         <v>31.02</v>
       </c>
       <c r="C21" t="n">
-        <v>31.47541242433202</v>
+        <v>31.05625979610119</v>
       </c>
       <c r="D21" t="n">
-        <v>0.4554124243320246</v>
+        <v>0.03625979610119501</v>
       </c>
       <c r="E21" t="n">
-        <v>0.207400476235972</v>
+        <v>0.001314772813300237</v>
       </c>
     </row>
     <row r="22">
@@ -803,13 +803,13 @@
         <v>31.12</v>
       </c>
       <c r="C22" t="n">
-        <v>31.90392191954129</v>
+        <v>31.21386468554301</v>
       </c>
       <c r="D22" t="n">
-        <v>0.7839219195412852</v>
+        <v>0.0938646855430072</v>
       </c>
       <c r="E22" t="n">
-        <v>0.6145335759372932</v>
+        <v>0.008810579192087624</v>
       </c>
     </row>
     <row r="23">
@@ -820,13 +820,13 @@
         <v>31.28</v>
       </c>
       <c r="C23" t="n">
-        <v>32.07101273992203</v>
+        <v>31.1276494698628</v>
       </c>
       <c r="D23" t="n">
-        <v>0.7910127399220315</v>
+        <v>-0.1523505301372055</v>
       </c>
       <c r="E23" t="n">
-        <v>0.6257011547189594</v>
+        <v>0.02321068403308755</v>
       </c>
     </row>
     <row r="24">
@@ -837,13 +837,13 @@
         <v>31.38</v>
       </c>
       <c r="C24" t="n">
-        <v>31.91345175328856</v>
+        <v>31.05959569874924</v>
       </c>
       <c r="D24" t="n">
-        <v>0.5334517532885563</v>
+        <v>-0.3204043012507576</v>
       </c>
       <c r="E24" t="n">
-        <v>0.2845707730866348</v>
+        <v>0.1026589162599862</v>
       </c>
     </row>
     <row r="25">
@@ -854,13 +854,13 @@
         <v>31.58</v>
       </c>
       <c r="C25" t="n">
-        <v>32.31898828666998</v>
+        <v>31.31717661401767</v>
       </c>
       <c r="D25" t="n">
-        <v>0.7389882866699793</v>
+        <v>-0.2628233859823261</v>
       </c>
       <c r="E25" t="n">
-        <v>0.5461036878354315</v>
+        <v>0.06907613221921478</v>
       </c>
     </row>
     <row r="26">
@@ -871,13 +871,13 @@
         <v>31.65</v>
       </c>
       <c r="C26" t="n">
-        <v>32.11056598256215</v>
+        <v>31.71826208678449</v>
       </c>
       <c r="D26" t="n">
-        <v>0.4605659825621515</v>
+        <v>0.06826208678449319</v>
       </c>
       <c r="E26" t="n">
-        <v>0.2121210242934401</v>
+        <v>0.00465971249217368</v>
       </c>
     </row>
     <row r="27">
@@ -888,13 +888,13 @@
         <v>31.88</v>
       </c>
       <c r="C27" t="n">
-        <v>32.74997155045387</v>
+        <v>32.51659351030031</v>
       </c>
       <c r="D27" t="n">
-        <v>0.8699715504538723</v>
+        <v>0.6365935103003117</v>
       </c>
       <c r="E27" t="n">
-        <v>0.7568504985991145</v>
+        <v>0.4052512973564731</v>
       </c>
     </row>
     <row r="28">
@@ -905,13 +905,13 @@
         <v>32.28</v>
       </c>
       <c r="C28" t="n">
-        <v>32.50279706675092</v>
+        <v>32.51662862662089</v>
       </c>
       <c r="D28" t="n">
-        <v>0.222797066750914</v>
+        <v>0.2366286266208846</v>
       </c>
       <c r="E28" t="n">
-        <v>0.04963853295281125</v>
+        <v>0.055993106936486</v>
       </c>
     </row>
     <row r="29">
@@ -922,13 +922,13 @@
         <v>32.45</v>
       </c>
       <c r="C29" t="n">
-        <v>32.61164882504537</v>
+        <v>32.8520766034088</v>
       </c>
       <c r="D29" t="n">
-        <v>0.1616488250453685</v>
+        <v>0.4020766034088012</v>
       </c>
       <c r="E29" t="n">
-        <v>0.02613034263854815</v>
+        <v>0.1616655950087584</v>
       </c>
     </row>
     <row r="30">
@@ -939,13 +939,13 @@
         <v>32.85</v>
       </c>
       <c r="C30" t="n">
-        <v>32.87701108739923</v>
+        <v>33.22228952033154</v>
       </c>
       <c r="D30" t="n">
-        <v>0.02701108739923086</v>
+        <v>0.3722895203315417</v>
       </c>
       <c r="E30" t="n">
-        <v>0.0007295988424888881</v>
+        <v>0.1385994869486894</v>
       </c>
     </row>
     <row r="31">
@@ -956,13 +956,13 @@
         <v>32.9</v>
       </c>
       <c r="C31" t="n">
-        <v>33.00066775366493</v>
+        <v>33.27917826661842</v>
       </c>
       <c r="D31" t="n">
-        <v>0.1006677536649292</v>
+        <v>0.3791782666184176</v>
       </c>
       <c r="E31" t="n">
-        <v>0.01013399662794287</v>
+        <v>0.1437761578757478</v>
       </c>
     </row>
     <row r="32">
@@ -973,13 +973,13 @@
         <v>33.1</v>
       </c>
       <c r="C32" t="n">
-        <v>32.97099385167881</v>
+        <v>33.34962080842794</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.1290061483211886</v>
+        <v>0.2496208084279417</v>
       </c>
       <c r="E32" t="n">
-        <v>0.01664258630466852</v>
+        <v>0.06231054800021914</v>
       </c>
     </row>
     <row r="33">
@@ -990,13 +990,13 @@
         <v>33.4</v>
       </c>
       <c r="C33" t="n">
-        <v>33.9102622668428</v>
+        <v>33.76405795937816</v>
       </c>
       <c r="D33" t="n">
-        <v>0.5102622668428012</v>
+        <v>0.3640579593781652</v>
       </c>
       <c r="E33" t="n">
-        <v>0.2603675809635541</v>
+        <v>0.1325381977865938</v>
       </c>
     </row>
     <row r="34">
@@ -1007,13 +1007,13 @@
         <v>33.7</v>
       </c>
       <c r="C34" t="n">
-        <v>33.79824511495674</v>
+        <v>33.76123245485297</v>
       </c>
       <c r="D34" t="n">
-        <v>0.09824511495673249</v>
+        <v>0.06123245485296991</v>
       </c>
       <c r="E34" t="n">
-        <v>0.009652102612861582</v>
+        <v>0.003749413527320998</v>
       </c>
     </row>
     <row r="35">
@@ -1024,13 +1024,13 @@
         <v>34.1</v>
       </c>
       <c r="C35" t="n">
-        <v>33.92622822892227</v>
+        <v>33.83241791371334</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.1737717710777318</v>
+        <v>-0.2675820862866587</v>
       </c>
       <c r="E35" t="n">
-        <v>0.03019662842349162</v>
+        <v>0.07160017290152086</v>
       </c>
     </row>
     <row r="36">
@@ -1041,13 +1041,13 @@
         <v>34.4</v>
       </c>
       <c r="C36" t="n">
-        <v>34.03392978109852</v>
+        <v>34.22622927822735</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.3660702189014771</v>
+        <v>-0.1737707217726481</v>
       </c>
       <c r="E36" t="n">
-        <v>0.1340074051665753</v>
+        <v>0.03019626374538707</v>
       </c>
     </row>
     <row r="37">
@@ -1058,13 +1058,13 @@
         <v>34.9</v>
       </c>
       <c r="C37" t="n">
-        <v>34.58591765730413</v>
+        <v>34.4503028803531</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.314082342695869</v>
+        <v>-0.4496971196468991</v>
       </c>
       <c r="E37" t="n">
-        <v>0.09864771799332529</v>
+        <v>0.2022274994187175</v>
       </c>
     </row>
     <row r="38">
@@ -1075,13 +1075,13 @@
         <v>35.3</v>
       </c>
       <c r="C38" t="n">
-        <v>35.70262508082213</v>
+        <v>35.51427435106902</v>
       </c>
       <c r="D38" t="n">
-        <v>0.4026250808221334</v>
+        <v>0.2142743510690224</v>
       </c>
       <c r="E38" t="n">
-        <v>0.1621069557070295</v>
+        <v>0.04591349752605065</v>
       </c>
     </row>
     <row r="39">
@@ -1092,13 +1092,13 @@
         <v>35.7</v>
       </c>
       <c r="C39" t="n">
-        <v>36.10905442207207</v>
+        <v>35.78944032712945</v>
       </c>
       <c r="D39" t="n">
-        <v>0.4090544220720673</v>
+        <v>0.08944032712945216</v>
       </c>
       <c r="E39" t="n">
-        <v>0.167325520216713</v>
+        <v>0.007999572117023415</v>
       </c>
     </row>
     <row r="40">
@@ -1109,13 +1109,13 @@
         <v>36.3</v>
       </c>
       <c r="C40" t="n">
-        <v>36.26659397241595</v>
+        <v>36.07524671403826</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.03340602758404998</v>
+        <v>-0.2247532859617394</v>
       </c>
       <c r="E40" t="n">
-        <v>0.001115962678946308</v>
+        <v>0.0505140395505994</v>
       </c>
     </row>
     <row r="41">
@@ -1126,13 +1126,13 @@
         <v>36.8</v>
       </c>
       <c r="C41" t="n">
-        <v>36.88279370718733</v>
+        <v>36.71440912003118</v>
       </c>
       <c r="D41" t="n">
-        <v>0.08279370718733503</v>
+        <v>-0.08559087996881232</v>
       </c>
       <c r="E41" t="n">
-        <v>0.006854797949822172</v>
+        <v>0.007325798733835638</v>
       </c>
     </row>
     <row r="42">
@@ -1143,13 +1143,13 @@
         <v>37.3</v>
       </c>
       <c r="C42" t="n">
-        <v>36.91183076134275</v>
+        <v>36.80509697398391</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.3881692386572482</v>
+        <v>-0.4949030260160896</v>
       </c>
       <c r="E42" t="n">
-        <v>0.1506753578397477</v>
+        <v>0.2449290051598823</v>
       </c>
     </row>
     <row r="43">
@@ -1160,13 +1160,13 @@
         <v>37.9</v>
       </c>
       <c r="C43" t="n">
-        <v>37.88692681021995</v>
+        <v>37.9356016899136</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.01307318978004446</v>
+        <v>0.03560168991360513</v>
       </c>
       <c r="E43" t="n">
-        <v>0.0001709082910250589</v>
+        <v>0.001267480324704493</v>
       </c>
     </row>
     <row r="44">
@@ -1177,13 +1177,13 @@
         <v>38.5</v>
       </c>
       <c r="C44" t="n">
-        <v>38.50346492903321</v>
+        <v>38.71469226868126</v>
       </c>
       <c r="D44" t="n">
-        <v>0.003464929033214048</v>
+        <v>0.2146922686812616</v>
       </c>
       <c r="E44" t="n">
-        <v>1.200573320520964e-05</v>
+        <v>0.04609277023150701</v>
       </c>
     </row>
     <row r="45">
@@ -1194,13 +1194,13 @@
         <v>38.9</v>
       </c>
       <c r="C45" t="n">
-        <v>38.8761424283309</v>
+        <v>39.11247680791239</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.02385757166909741</v>
+        <v>0.2124768079123882</v>
       </c>
       <c r="E45" t="n">
-        <v>0.0005691837259461194</v>
+        <v>0.04514639390063792</v>
       </c>
     </row>
     <row r="46">
@@ -1211,13 +1211,13 @@
         <v>39.4</v>
       </c>
       <c r="C46" t="n">
-        <v>39.2557687270679</v>
+        <v>39.5334708992003</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.1442312729321031</v>
+        <v>0.1334708992002973</v>
       </c>
       <c r="E46" t="n">
-        <v>0.02080266009161483</v>
+        <v>0.01781448093333593</v>
       </c>
     </row>
     <row r="47">
@@ -1228,13 +1228,13 @@
         <v>39.9</v>
       </c>
       <c r="C47" t="n">
-        <v>39.56415861988053</v>
+        <v>39.7926743465075</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.3358413801194686</v>
+        <v>-0.1073256534924951</v>
       </c>
       <c r="E47" t="n">
-        <v>0.1127894326005494</v>
+        <v>0.01151879589759113</v>
       </c>
     </row>
     <row r="48">
@@ -1245,13 +1245,13 @@
         <v>40.1</v>
       </c>
       <c r="C48" t="n">
-        <v>39.79025351510796</v>
+        <v>40.15851467971533</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.3097464848920453</v>
+        <v>0.05851467971532998</v>
       </c>
       <c r="E48" t="n">
-        <v>0.09594288490297802</v>
+        <v>0.003423967742187649</v>
       </c>
     </row>
     <row r="49">
@@ -1262,13 +1262,13 @@
         <v>40.6</v>
       </c>
       <c r="C49" t="n">
-        <v>40.01247792801502</v>
+        <v>40.4026953359831</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.5875220719849779</v>
+        <v>-0.1973046640168974</v>
       </c>
       <c r="E49" t="n">
-        <v>0.3451821850695215</v>
+        <v>0.03892913044282077</v>
       </c>
     </row>
     <row r="50">
@@ -1279,13 +1279,13 @@
         <v>40.9</v>
       </c>
       <c r="C50" t="n">
-        <v>40.31626741864778</v>
+        <v>40.73678562107821</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.5837325813522227</v>
+        <v>-0.1632143789217864</v>
       </c>
       <c r="E50" t="n">
-        <v>0.3407437265321293</v>
+        <v>0.02663893348682446</v>
       </c>
     </row>
     <row r="51">
@@ -1296,13 +1296,13 @@
         <v>41.2</v>
       </c>
       <c r="C51" t="n">
-        <v>41.48393709049734</v>
+        <v>41.92965063556335</v>
       </c>
       <c r="D51" t="n">
-        <v>0.2839370904973393</v>
+        <v>0.7296506355633454</v>
       </c>
       <c r="E51" t="n">
-        <v>0.08062027136009424</v>
+        <v>0.5323900499779939</v>
       </c>
     </row>
     <row r="52">
@@ -1313,11 +1313,11 @@
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="n">
-        <v>-1.879335802740034</v>
+        <v>-0.09224097631917516</v>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="n">
-        <v>11.20725098580535</v>
+        <v>4.780329254034106</v>
       </c>
     </row>
     <row r="53">
@@ -1330,7 +1330,7 @@
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="n">
-        <v>0.2241450197161069</v>
+        <v>0.09560658508068212</v>
       </c>
     </row>
   </sheetData>

--- a/partial/sliding_window_results_window_3.xlsx
+++ b/partial/sliding_window_results_window_3.xlsx
@@ -463,13 +463,13 @@
         <v>29.35</v>
       </c>
       <c r="C2" t="n">
-        <v>30.08906540050407</v>
+        <v>29.35193956677075</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7390654005040673</v>
+        <v>0.001939566770747803</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5462176662222374</v>
+        <v>3.761919258189059e-06</v>
       </c>
     </row>
     <row r="3">
@@ -480,13 +480,13 @@
         <v>29.37</v>
       </c>
       <c r="C3" t="n">
-        <v>29.78556385453234</v>
+        <v>29.21437380161757</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4155638545323406</v>
+        <v>-0.1556261983824356</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1726933171937763</v>
+        <v>0.02421951362296921</v>
       </c>
     </row>
     <row r="4">
@@ -497,13 +497,13 @@
         <v>29.54</v>
       </c>
       <c r="C4" t="n">
-        <v>29.2700097296191</v>
+        <v>28.83226680802768</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.2699902703808945</v>
+        <v>-0.70773319197232</v>
       </c>
       <c r="E4" t="n">
-        <v>0.07289474610034853</v>
+        <v>0.5008862710193287</v>
       </c>
     </row>
     <row r="5">
@@ -514,13 +514,13 @@
         <v>29.55</v>
       </c>
       <c r="C5" t="n">
-        <v>29.82163104762523</v>
+        <v>29.55249631747839</v>
       </c>
       <c r="D5" t="n">
-        <v>0.271631047625231</v>
+        <v>0.002496317478385635</v>
       </c>
       <c r="E5" t="n">
-        <v>0.07378342603398054</v>
+        <v>6.231600952893613e-06</v>
       </c>
     </row>
     <row r="6">
@@ -531,13 +531,13 @@
         <v>29.75</v>
       </c>
       <c r="C6" t="n">
-        <v>29.50887915476766</v>
+        <v>29.49929484114895</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.2411208452323379</v>
+        <v>-0.2507051588510514</v>
       </c>
       <c r="E6" t="n">
-        <v>0.05813926200555704</v>
+        <v>0.06285307667453091</v>
       </c>
     </row>
     <row r="7">
@@ -548,13 +548,13 @@
         <v>29.84</v>
       </c>
       <c r="C7" t="n">
-        <v>30.0574479233339</v>
+        <v>30.07502798186751</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2174479233338964</v>
+        <v>0.2350279818675141</v>
       </c>
       <c r="E7" t="n">
-        <v>0.04728359936222409</v>
+        <v>0.05523815226071652</v>
       </c>
     </row>
     <row r="8">
@@ -565,13 +565,13 @@
         <v>29.81</v>
       </c>
       <c r="C8" t="n">
-        <v>29.93957089088588</v>
+        <v>29.94560540298474</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1295708908858764</v>
+        <v>0.1356054029847442</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01678861576495968</v>
+        <v>0.01838882531865487</v>
       </c>
     </row>
     <row r="9">
@@ -582,13 +582,13 @@
         <v>29.92</v>
       </c>
       <c r="C9" t="n">
-        <v>29.68718008544232</v>
+        <v>29.90212544728803</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.2328199145576804</v>
+        <v>-0.01787455271196947</v>
       </c>
       <c r="E9" t="n">
-        <v>0.05420511261464558</v>
+        <v>0.0003194996346529752</v>
       </c>
     </row>
     <row r="10">
@@ -599,13 +599,13 @@
         <v>29.98</v>
       </c>
       <c r="C10" t="n">
-        <v>29.61174624372592</v>
+        <v>29.61964560462208</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.3682537562740791</v>
+        <v>-0.3603543953779251</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1356108290099688</v>
+        <v>0.12985529026819</v>
       </c>
     </row>
     <row r="11">
@@ -616,13 +616,13 @@
         <v>30.04</v>
       </c>
       <c r="C11" t="n">
-        <v>29.61864572433147</v>
+        <v>29.86945853965221</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.4213542756685307</v>
+        <v>-0.1705414603477919</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1775394256241521</v>
+        <v>0.02908438969755749</v>
       </c>
     </row>
     <row r="12">
@@ -633,13 +633,13 @@
         <v>30.21</v>
       </c>
       <c r="C12" t="n">
-        <v>29.69651013084202</v>
+        <v>29.77603459046486</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.5134898691579828</v>
+        <v>-0.4339654095351406</v>
       </c>
       <c r="E12" t="n">
-        <v>0.2636718457278823</v>
+        <v>0.1883259766730023</v>
       </c>
     </row>
     <row r="13">
@@ -650,13 +650,13 @@
         <v>30.22</v>
       </c>
       <c r="C13" t="n">
-        <v>29.9117261406573</v>
+        <v>30.02058903458105</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.3082738593426946</v>
+        <v>-0.1994109654189522</v>
       </c>
       <c r="E13" t="n">
-        <v>0.09503277235403944</v>
+        <v>0.03976473312931855</v>
       </c>
     </row>
     <row r="14">
@@ -667,13 +667,13 @@
         <v>30.38</v>
       </c>
       <c r="C14" t="n">
-        <v>30.20390420453156</v>
+        <v>30.09021846068341</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.1760957954684379</v>
+        <v>-0.2897815393165857</v>
       </c>
       <c r="E14" t="n">
-        <v>0.03100972918166191</v>
+        <v>0.08397334052868989</v>
       </c>
     </row>
     <row r="15">
@@ -684,13 +684,13 @@
         <v>30.44</v>
       </c>
       <c r="C15" t="n">
-        <v>30.46567407497348</v>
+        <v>30.53938103941733</v>
       </c>
       <c r="D15" t="n">
-        <v>0.02567407497347673</v>
+        <v>0.0993810394173309</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0006591581257437044</v>
+        <v>0.009876590995669078</v>
       </c>
     </row>
     <row r="16">
@@ -701,13 +701,13 @@
         <v>30.48</v>
       </c>
       <c r="C16" t="n">
-        <v>30.22834259137082</v>
+        <v>30.35662006040967</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.2516574086291818</v>
+        <v>-0.123379939590329</v>
       </c>
       <c r="E16" t="n">
-        <v>0.06333145131795501</v>
+        <v>0.01522260949331323</v>
       </c>
     </row>
     <row r="17">
@@ -718,13 +718,13 @@
         <v>30.69</v>
       </c>
       <c r="C17" t="n">
-        <v>30.26397303977103</v>
+        <v>30.42029207319887</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.4260269602289668</v>
+        <v>-0.2697079268011358</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1814989708419337</v>
+        <v>0.0727423657793668</v>
       </c>
     </row>
     <row r="18">
@@ -735,13 +735,13 @@
         <v>30.75</v>
       </c>
       <c r="C18" t="n">
-        <v>30.78538835040724</v>
+        <v>30.50635504274393</v>
       </c>
       <c r="D18" t="n">
-        <v>0.03538835040723853</v>
+        <v>-0.2436449572560662</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0012523353445455</v>
+        <v>0.05936286519631031</v>
       </c>
     </row>
     <row r="19">
@@ -752,13 +752,13 @@
         <v>30.94</v>
       </c>
       <c r="C19" t="n">
-        <v>30.67079586766802</v>
+        <v>30.57433543785837</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2692041323319856</v>
+        <v>-0.3656645621416317</v>
       </c>
       <c r="E19" t="n">
-        <v>0.07247086486461721</v>
+        <v>0.1337105720062312</v>
       </c>
     </row>
     <row r="20">
@@ -769,13 +769,13 @@
         <v>30.95</v>
       </c>
       <c r="C20" t="n">
-        <v>30.81323862459335</v>
+        <v>30.69329430211953</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1367613754066461</v>
+        <v>-0.2567056978804736</v>
       </c>
       <c r="E20" t="n">
-        <v>0.01870367380311759</v>
+        <v>0.06589781532430099</v>
       </c>
     </row>
     <row r="21">
@@ -786,13 +786,13 @@
         <v>31.02</v>
       </c>
       <c r="C21" t="n">
-        <v>31.05625979610119</v>
+        <v>31.05811356346379</v>
       </c>
       <c r="D21" t="n">
-        <v>0.03625979610119501</v>
+        <v>0.03811356346378858</v>
       </c>
       <c r="E21" t="n">
-        <v>0.001314772813300237</v>
+        <v>0.00145264371990824</v>
       </c>
     </row>
     <row r="22">
@@ -803,13 +803,13 @@
         <v>31.12</v>
       </c>
       <c r="C22" t="n">
-        <v>31.21386468554301</v>
+        <v>31.29795155194756</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0938646855430072</v>
+        <v>0.1779515519475581</v>
       </c>
       <c r="E22" t="n">
-        <v>0.008810579192087624</v>
+        <v>0.03166675484054446</v>
       </c>
     </row>
     <row r="23">
@@ -820,13 +820,13 @@
         <v>31.28</v>
       </c>
       <c r="C23" t="n">
-        <v>31.1276494698628</v>
+        <v>31.36738222176833</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1523505301372055</v>
+        <v>0.08738222176833332</v>
       </c>
       <c r="E23" t="n">
-        <v>0.02321068403308755</v>
+        <v>0.007635652681170186</v>
       </c>
     </row>
     <row r="24">
@@ -837,13 +837,13 @@
         <v>31.38</v>
       </c>
       <c r="C24" t="n">
-        <v>31.05959569874924</v>
+        <v>31.36768915482794</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.3204043012507576</v>
+        <v>-0.01231084517205971</v>
       </c>
       <c r="E24" t="n">
-        <v>0.1026589162599862</v>
+        <v>0.000151556908850426</v>
       </c>
     </row>
     <row r="25">
@@ -854,13 +854,13 @@
         <v>31.58</v>
       </c>
       <c r="C25" t="n">
-        <v>31.31717661401767</v>
+        <v>31.67432772299919</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.2628233859823261</v>
+        <v>0.09432772299919279</v>
       </c>
       <c r="E25" t="n">
-        <v>0.06907613221921478</v>
+        <v>0.008897719326212444</v>
       </c>
     </row>
     <row r="26">
@@ -871,13 +871,13 @@
         <v>31.65</v>
       </c>
       <c r="C26" t="n">
-        <v>31.71826208678449</v>
+        <v>31.52929375692791</v>
       </c>
       <c r="D26" t="n">
-        <v>0.06826208678449319</v>
+        <v>-0.1207062430720889</v>
       </c>
       <c r="E26" t="n">
-        <v>0.00465971249217368</v>
+        <v>0.0145699971165782</v>
       </c>
     </row>
     <row r="27">
@@ -888,13 +888,13 @@
         <v>31.88</v>
       </c>
       <c r="C27" t="n">
-        <v>32.51659351030031</v>
+        <v>32.05817207035469</v>
       </c>
       <c r="D27" t="n">
-        <v>0.6365935103003117</v>
+        <v>0.1781720703546874</v>
       </c>
       <c r="E27" t="n">
-        <v>0.4052512973564731</v>
+        <v>0.03174528665447568</v>
       </c>
     </row>
     <row r="28">
@@ -905,13 +905,13 @@
         <v>32.28</v>
       </c>
       <c r="C28" t="n">
-        <v>32.51662862662089</v>
+        <v>31.99931417276246</v>
       </c>
       <c r="D28" t="n">
-        <v>0.2366286266208846</v>
+        <v>-0.2806858272375372</v>
       </c>
       <c r="E28" t="n">
-        <v>0.055993106936486</v>
+        <v>0.07878453361202059</v>
       </c>
     </row>
     <row r="29">
@@ -922,13 +922,13 @@
         <v>32.45</v>
       </c>
       <c r="C29" t="n">
-        <v>32.8520766034088</v>
+        <v>32.26217945847518</v>
       </c>
       <c r="D29" t="n">
-        <v>0.4020766034088012</v>
+        <v>-0.1878205415248217</v>
       </c>
       <c r="E29" t="n">
-        <v>0.1616655950087584</v>
+        <v>0.03527655581867729</v>
       </c>
     </row>
     <row r="30">
@@ -939,13 +939,13 @@
         <v>32.85</v>
       </c>
       <c r="C30" t="n">
-        <v>33.22228952033154</v>
+        <v>32.92548277767714</v>
       </c>
       <c r="D30" t="n">
-        <v>0.3722895203315417</v>
+        <v>0.07548277767713785</v>
       </c>
       <c r="E30" t="n">
-        <v>0.1385994869486894</v>
+        <v>0.00569764972585622</v>
       </c>
     </row>
     <row r="31">
@@ -956,13 +956,13 @@
         <v>32.9</v>
       </c>
       <c r="C31" t="n">
-        <v>33.27917826661842</v>
+        <v>33.07522983770523</v>
       </c>
       <c r="D31" t="n">
-        <v>0.3791782666184176</v>
+        <v>0.1752298377052313</v>
       </c>
       <c r="E31" t="n">
-        <v>0.1437761578757478</v>
+        <v>0.03070549602220169</v>
       </c>
     </row>
     <row r="32">
@@ -973,13 +973,13 @@
         <v>33.1</v>
       </c>
       <c r="C32" t="n">
-        <v>33.34962080842794</v>
+        <v>32.91606219589418</v>
       </c>
       <c r="D32" t="n">
-        <v>0.2496208084279417</v>
+        <v>-0.1839378041058239</v>
       </c>
       <c r="E32" t="n">
-        <v>0.06231054800021914</v>
+        <v>0.03383311577927246</v>
       </c>
     </row>
     <row r="33">
@@ -990,13 +990,13 @@
         <v>33.4</v>
       </c>
       <c r="C33" t="n">
-        <v>33.76405795937816</v>
+        <v>33.61455988603146</v>
       </c>
       <c r="D33" t="n">
-        <v>0.3640579593781652</v>
+        <v>0.2145598860314593</v>
       </c>
       <c r="E33" t="n">
-        <v>0.1325381977865938</v>
+        <v>0.04603594469383279</v>
       </c>
     </row>
     <row r="34">
@@ -1007,13 +1007,13 @@
         <v>33.7</v>
       </c>
       <c r="C34" t="n">
-        <v>33.76123245485297</v>
+        <v>33.4697501130027</v>
       </c>
       <c r="D34" t="n">
-        <v>0.06123245485296991</v>
+        <v>-0.2302498869972993</v>
       </c>
       <c r="E34" t="n">
-        <v>0.003749413527320998</v>
+        <v>0.05301501046226911</v>
       </c>
     </row>
     <row r="35">
@@ -1024,13 +1024,13 @@
         <v>34.1</v>
       </c>
       <c r="C35" t="n">
-        <v>33.83241791371334</v>
+        <v>33.69267542063439</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.2675820862866587</v>
+        <v>-0.4073245793656142</v>
       </c>
       <c r="E35" t="n">
-        <v>0.07160017290152086</v>
+        <v>0.1659133129553745</v>
       </c>
     </row>
     <row r="36">
@@ -1041,13 +1041,13 @@
         <v>34.4</v>
       </c>
       <c r="C36" t="n">
-        <v>34.22622927822735</v>
+        <v>34.10827338862551</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.1737707217726481</v>
+        <v>-0.291726611374493</v>
       </c>
       <c r="E36" t="n">
-        <v>0.03019626374538707</v>
+        <v>0.08510441578404444</v>
       </c>
     </row>
     <row r="37">
@@ -1058,13 +1058,13 @@
         <v>34.9</v>
       </c>
       <c r="C37" t="n">
-        <v>34.4503028803531</v>
+        <v>34.73577032384009</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.4496971196468991</v>
+        <v>-0.1642296761599056</v>
       </c>
       <c r="E37" t="n">
-        <v>0.2022274994187175</v>
+        <v>0.02697138653158746</v>
       </c>
     </row>
     <row r="38">
@@ -1075,13 +1075,13 @@
         <v>35.3</v>
       </c>
       <c r="C38" t="n">
-        <v>35.51427435106902</v>
+        <v>35.49741061440871</v>
       </c>
       <c r="D38" t="n">
-        <v>0.2142743510690224</v>
+        <v>0.1974106144087102</v>
       </c>
       <c r="E38" t="n">
-        <v>0.04591349752605065</v>
+        <v>0.03897095068122446</v>
       </c>
     </row>
     <row r="39">
@@ -1092,13 +1092,13 @@
         <v>35.7</v>
       </c>
       <c r="C39" t="n">
-        <v>35.78944032712945</v>
+        <v>35.75845614006425</v>
       </c>
       <c r="D39" t="n">
-        <v>0.08944032712945216</v>
+        <v>0.05845614006424427</v>
       </c>
       <c r="E39" t="n">
-        <v>0.007999572117023415</v>
+        <v>0.003417120311210543</v>
       </c>
     </row>
     <row r="40">
@@ -1109,13 +1109,13 @@
         <v>36.3</v>
       </c>
       <c r="C40" t="n">
-        <v>36.07524671403826</v>
+        <v>36.2345356988731</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.2247532859617394</v>
+        <v>-0.0654643011268945</v>
       </c>
       <c r="E40" t="n">
-        <v>0.0505140395505994</v>
+        <v>0.00428557472203272</v>
       </c>
     </row>
     <row r="41">
@@ -1126,13 +1126,13 @@
         <v>36.8</v>
       </c>
       <c r="C41" t="n">
-        <v>36.71440912003118</v>
+        <v>36.72916351564232</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.08559087996881232</v>
+        <v>-0.07083648435767742</v>
       </c>
       <c r="E41" t="n">
-        <v>0.007325798733835638</v>
+        <v>0.005017807516155478</v>
       </c>
     </row>
     <row r="42">
@@ -1143,13 +1143,13 @@
         <v>37.3</v>
       </c>
       <c r="C42" t="n">
-        <v>36.80509697398391</v>
+        <v>36.88095081143874</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.4949030260160896</v>
+        <v>-0.4190491885612531</v>
       </c>
       <c r="E42" t="n">
-        <v>0.2449290051598823</v>
+        <v>0.1756022224338446</v>
       </c>
     </row>
     <row r="43">
@@ -1160,13 +1160,13 @@
         <v>37.9</v>
       </c>
       <c r="C43" t="n">
-        <v>37.9356016899136</v>
+        <v>37.50648263314267</v>
       </c>
       <c r="D43" t="n">
-        <v>0.03560168991360513</v>
+        <v>-0.3935173668573242</v>
       </c>
       <c r="E43" t="n">
-        <v>0.001267480324704493</v>
+        <v>0.1548559180183219</v>
       </c>
     </row>
     <row r="44">
@@ -1177,13 +1177,13 @@
         <v>38.5</v>
       </c>
       <c r="C44" t="n">
-        <v>38.71469226868126</v>
+        <v>38.35547050083341</v>
       </c>
       <c r="D44" t="n">
-        <v>0.2146922686812616</v>
+        <v>-0.1445294991665946</v>
       </c>
       <c r="E44" t="n">
-        <v>0.04609277023150701</v>
+        <v>0.02088877612934668</v>
       </c>
     </row>
     <row r="45">
@@ -1194,13 +1194,13 @@
         <v>38.9</v>
       </c>
       <c r="C45" t="n">
-        <v>39.11247680791239</v>
+        <v>38.8651584375132</v>
       </c>
       <c r="D45" t="n">
-        <v>0.2124768079123882</v>
+        <v>-0.03484156248679682</v>
       </c>
       <c r="E45" t="n">
-        <v>0.04514639390063792</v>
+        <v>0.001213934476521367</v>
       </c>
     </row>
     <row r="46">
@@ -1211,13 +1211,13 @@
         <v>39.4</v>
       </c>
       <c r="C46" t="n">
-        <v>39.5334708992003</v>
+        <v>39.29905314489192</v>
       </c>
       <c r="D46" t="n">
-        <v>0.1334708992002973</v>
+        <v>-0.1009468551080772</v>
       </c>
       <c r="E46" t="n">
-        <v>0.01781448093333593</v>
+        <v>0.01019026755621114</v>
       </c>
     </row>
     <row r="47">
@@ -1228,13 +1228,13 @@
         <v>39.9</v>
       </c>
       <c r="C47" t="n">
-        <v>39.7926743465075</v>
+        <v>39.82081235214797</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.1073256534924951</v>
+        <v>-0.0791876478520237</v>
       </c>
       <c r="E47" t="n">
-        <v>0.01151879589759113</v>
+        <v>0.006270683572336114</v>
       </c>
     </row>
     <row r="48">
@@ -1245,13 +1245,13 @@
         <v>40.1</v>
       </c>
       <c r="C48" t="n">
-        <v>40.15851467971533</v>
+        <v>39.86061441401134</v>
       </c>
       <c r="D48" t="n">
-        <v>0.05851467971532998</v>
+        <v>-0.2393855859886642</v>
       </c>
       <c r="E48" t="n">
-        <v>0.003423967742187649</v>
+        <v>0.05730545877913615</v>
       </c>
     </row>
     <row r="49">
@@ -1262,13 +1262,13 @@
         <v>40.6</v>
       </c>
       <c r="C49" t="n">
-        <v>40.4026953359831</v>
+        <v>40.05889047614647</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.1973046640168974</v>
+        <v>-0.5411095238535353</v>
       </c>
       <c r="E49" t="n">
-        <v>0.03892913044282077</v>
+        <v>0.2927995168049997</v>
       </c>
     </row>
     <row r="50">
@@ -1279,13 +1279,13 @@
         <v>40.9</v>
       </c>
       <c r="C50" t="n">
-        <v>40.73678562107821</v>
+        <v>40.38083114168604</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.1632143789217864</v>
+        <v>-0.5191688583139538</v>
       </c>
       <c r="E50" t="n">
-        <v>0.02663893348682446</v>
+        <v>0.2695363034430142</v>
       </c>
     </row>
     <row r="51">
@@ -1296,13 +1296,13 @@
         <v>41.2</v>
       </c>
       <c r="C51" t="n">
-        <v>41.92965063556335</v>
+        <v>41.88798926946445</v>
       </c>
       <c r="D51" t="n">
-        <v>0.7296506355633454</v>
+        <v>0.6879892694644454</v>
       </c>
       <c r="E51" t="n">
-        <v>0.5323900499779939</v>
+        <v>0.4733292348982213</v>
       </c>
     </row>
     <row r="52">
@@ -1313,11 +1313,11 @@
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="n">
-        <v>-0.09224097631917516</v>
+        <v>-5.872598879862736</v>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="n">
-        <v>4.780329254034106</v>
+        <v>3.660872683118467</v>
       </c>
     </row>
     <row r="53">
@@ -1330,7 +1330,7 @@
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="n">
-        <v>0.09560658508068212</v>
+        <v>0.07321745366236934</v>
       </c>
     </row>
   </sheetData>
